--- a/docs/PRAP_UI_Component_List_v2.5.xlsx
+++ b/docs/PRAP_UI_Component_List_v2.5.xlsx
@@ -2080,7 +2080,7 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>First panel on the tab. Duration under each name, bands coloured by period, milestone markers.</t>
+          <t>First panel on the tab. Duration under each name, bands gray unless the period is given a colour (R-59), milestone markers.</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
@@ -4897,7 +4897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5146,8 +5146,40 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>O-10 colour rule</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>SUPERSEDED</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>R-59</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>A period is drawn in the colour chosen for it in the Periods table's Highlight column, and gray when none is chosen; weight still shades it. The per-period-name hues are retired.</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Plan v2.70, change R-59</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Nothing else in the plan or specification moved. Everything else you asked for was a design change the existing requirements already permitted.</t>
         </is>
